--- a/data/trans_orig/P21_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82220</t>
+          <t>80104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117964</t>
+          <t>117020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94095</t>
+          <t>95313</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132472</t>
+          <t>128064</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185266</t>
+          <t>186753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236059</t>
+          <t>234556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376100</t>
+          <t>377044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>411844</t>
+          <t>413960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334077</t>
+          <t>338485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>372454</t>
+          <t>371236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>724554</t>
+          <t>726057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775347</t>
+          <t>773860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94138</t>
+          <t>92549</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134091</t>
+          <t>131353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160810</t>
+          <t>162625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>209798</t>
+          <t>208996</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>267627</t>
+          <t>265330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>328668</t>
+          <t>327163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>601398</t>
+          <t>604136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>641351</t>
+          <t>642940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415696</t>
+          <t>416498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>464684</t>
+          <t>462869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1032314</t>
+          <t>1033819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1093355</t>
+          <t>1095652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72650</t>
+          <t>73625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110315</t>
+          <t>109469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116236</t>
+          <t>116219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160787</t>
+          <t>156631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200106</t>
+          <t>200867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256045</t>
+          <t>257335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527468</t>
+          <t>528314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>565133</t>
+          <t>564158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>528957</t>
+          <t>533113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>573508</t>
+          <t>573525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1071482</t>
+          <t>1070192</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1127421</t>
+          <t>1126660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64969</t>
+          <t>65597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100528</t>
+          <t>98175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87228</t>
+          <t>86125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123839</t>
+          <t>122618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160357</t>
+          <t>156925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209623</t>
+          <t>208123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>418619</t>
+          <t>420972</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454178</t>
+          <t>453550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>391803</t>
+          <t>393024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>428414</t>
+          <t>429517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>825166</t>
+          <t>826666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>874432</t>
+          <t>877864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48930</t>
+          <t>49383</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78566</t>
+          <t>78178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70135</t>
+          <t>72235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103099</t>
+          <t>102769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127984</t>
+          <t>127272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173452</t>
+          <t>174708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308144</t>
+          <t>308532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337780</t>
+          <t>337327</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>300887</t>
+          <t>301217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>333851</t>
+          <t>331751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>617244</t>
+          <t>615988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>662712</t>
+          <t>663424</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,9%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46950</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74107</t>
+          <t>75724</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77962</t>
+          <t>80799</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111139</t>
+          <t>112201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135280</t>
+          <t>136916</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176449</t>
+          <t>177051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218476</t>
+          <t>216859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245633</t>
+          <t>243265</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231795</t>
+          <t>230733</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264972</t>
+          <t>262135</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>459068</t>
+          <t>458466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500237</t>
+          <t>498601</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44696</t>
+          <t>44093</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69012</t>
+          <t>70887</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88064</t>
+          <t>87937</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123350</t>
+          <t>123787</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>140074</t>
+          <t>139845</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186776</t>
+          <t>183528</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>140871</t>
+          <t>138996</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165187</t>
+          <t>165790</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>210558</t>
+          <t>210121</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>245844</t>
+          <t>245971</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>357015</t>
+          <t>360263</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>403717</t>
+          <t>403946</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>521268</t>
+          <t>515224</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>607385</t>
+          <t>602739</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>774989</t>
+          <t>774864</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>873724</t>
+          <t>872861</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1317955</t>
+          <t>1319432</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1449133</t>
+          <t>1450792</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2668274</t>
+          <t>2672920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2754391</t>
+          <t>2760435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2504533</t>
+          <t>2505396</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2603268</t>
+          <t>2603393</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5204782</t>
+          <t>5203123</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5335960</t>
+          <t>5334483</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91258</t>
+          <t>92812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127818</t>
+          <t>128253</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111045</t>
+          <t>109773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149196</t>
+          <t>149749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>212546</t>
+          <t>210436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>263633</t>
+          <t>266115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325374</t>
+          <t>324939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>361934</t>
+          <t>360380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281034</t>
+          <t>280481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>319185</t>
+          <t>320457</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>619789</t>
+          <t>617307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>670876</t>
+          <t>672986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140458</t>
+          <t>140935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184019</t>
+          <t>186611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190569</t>
+          <t>191318</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>238091</t>
+          <t>240973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>346563</t>
+          <t>342565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408708</t>
+          <t>408251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>503068</t>
+          <t>500476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>546629</t>
+          <t>546152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371196</t>
+          <t>368314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>418718</t>
+          <t>417969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887666</t>
+          <t>888123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>949811</t>
+          <t>953809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105399</t>
+          <t>105464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146287</t>
+          <t>148163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147684</t>
+          <t>147817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>191810</t>
+          <t>195835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262626</t>
+          <t>266597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>328225</t>
+          <t>330498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534849</t>
+          <t>532973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>575737</t>
+          <t>575672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>517862</t>
+          <t>513837</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>561988</t>
+          <t>561855</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1062582</t>
+          <t>1060309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1128181</t>
+          <t>1124210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81987</t>
+          <t>81820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118734</t>
+          <t>118710</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108223</t>
+          <t>108998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151166</t>
+          <t>153180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>201598</t>
+          <t>200264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>259372</t>
+          <t>258556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>495883</t>
+          <t>495907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>532630</t>
+          <t>532797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464074</t>
+          <t>462060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>507017</t>
+          <t>506242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>970485</t>
+          <t>971301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1028259</t>
+          <t>1029593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,72%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93002</t>
+          <t>93200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88080</t>
+          <t>86521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122463</t>
+          <t>123561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156874</t>
+          <t>153622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205267</t>
+          <t>203119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336427</t>
+          <t>336229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>368713</t>
+          <t>369087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>325337</t>
+          <t>324239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>359720</t>
+          <t>361279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>671962</t>
+          <t>674110</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>720355</t>
+          <t>723607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41289</t>
+          <t>43051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71616</t>
+          <t>73665</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75380</t>
+          <t>76710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108097</t>
+          <t>111620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127316</t>
+          <t>126363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171934</t>
+          <t>170467</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237170</t>
+          <t>235121</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267497</t>
+          <t>265735</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245899</t>
+          <t>242376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278616</t>
+          <t>277286</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490848</t>
+          <t>492315</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535466</t>
+          <t>536419</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62313</t>
+          <t>61443</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95496</t>
+          <t>92249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124724</t>
+          <t>123389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163907</t>
+          <t>160588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>195655</t>
+          <t>197124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>244154</t>
+          <t>247137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>154355</t>
+          <t>157602</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187538</t>
+          <t>188408</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>225072</t>
+          <t>228391</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>264255</t>
+          <t>265590</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>394676</t>
+          <t>391693</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>443175</t>
+          <t>441706</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>658662</t>
+          <t>660984</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>759263</t>
+          <t>758293</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>927222</t>
+          <t>928969</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1038189</t>
+          <t>1042891</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1615706</t>
+          <t>1614116</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1763105</t>
+          <t>1764599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2664835</t>
+          <t>2665805</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2765436</t>
+          <t>2763114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2517014</t>
+          <t>2512312</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2627981</t>
+          <t>2626234</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5216196</t>
+          <t>5214702</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5363595</t>
+          <t>5365185</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76425</t>
+          <t>75758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109990</t>
+          <t>112250</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78095</t>
+          <t>77246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111239</t>
+          <t>111739</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165576</t>
+          <t>166434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213475</t>
+          <t>214114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309473</t>
+          <t>307213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>343038</t>
+          <t>343705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284516</t>
+          <t>284016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>317660</t>
+          <t>318509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>601743</t>
+          <t>601104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>649642</t>
+          <t>648784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79043</t>
+          <t>78363</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117222</t>
+          <t>114630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120428</t>
+          <t>120073</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161634</t>
+          <t>160943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>210954</t>
+          <t>208094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>267079</t>
+          <t>266653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>470062</t>
+          <t>472654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508241</t>
+          <t>508921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401025</t>
+          <t>401716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442231</t>
+          <t>442586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>882865</t>
+          <t>883291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>938990</t>
+          <t>941850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89659</t>
+          <t>90282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127425</t>
+          <t>130091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121358</t>
+          <t>124038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162903</t>
+          <t>163647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221157</t>
+          <t>221865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278222</t>
+          <t>280118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539116</t>
+          <t>536450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>576882</t>
+          <t>576259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>497615</t>
+          <t>496871</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539160</t>
+          <t>536480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1048837</t>
+          <t>1046941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1105902</t>
+          <t>1105194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72866</t>
+          <t>73743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110303</t>
+          <t>110299</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97225</t>
+          <t>97200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137743</t>
+          <t>137615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181286</t>
+          <t>181933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236758</t>
+          <t>239056</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>533712</t>
+          <t>533716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>571149</t>
+          <t>570272</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>511334</t>
+          <t>511462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>551852</t>
+          <t>551877</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1056334</t>
+          <t>1054036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1111806</t>
+          <t>1111159</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58423</t>
+          <t>58714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91577</t>
+          <t>89471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72662</t>
+          <t>73130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108207</t>
+          <t>109664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138386</t>
+          <t>141031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>187488</t>
+          <t>190189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>384414</t>
+          <t>386520</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>417568</t>
+          <t>417277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386823</t>
+          <t>385366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>422368</t>
+          <t>421900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>783533</t>
+          <t>780832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>832635</t>
+          <t>829990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43170</t>
+          <t>44026</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71148</t>
+          <t>71844</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63739</t>
+          <t>64974</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96515</t>
+          <t>98735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116017</t>
+          <t>116518</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>158192</t>
+          <t>159494</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262244</t>
+          <t>261548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290222</t>
+          <t>289366</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>279631</t>
+          <t>277411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312407</t>
+          <t>311172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>551346</t>
+          <t>550044</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>593521</t>
+          <t>593020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57230</t>
+          <t>57544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80182</t>
+          <t>80201</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>119895</t>
+          <t>119330</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121848</t>
+          <t>121168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166735</t>
+          <t>168099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199768</t>
+          <t>199454</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>221319</t>
+          <t>222461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>279003</t>
+          <t>279568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318716</t>
+          <t>318697</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>489161</t>
+          <t>487797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>534048</t>
+          <t>534728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>518647</t>
+          <t>521233</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>608351</t>
+          <t>605503</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>710011</t>
+          <t>714275</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>809947</t>
+          <t>817333</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1257784</t>
+          <t>1256781</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1393367</t>
+          <t>1391939</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2775333</t>
+          <t>2778181</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2865037</t>
+          <t>2862451</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2728136</t>
+          <t>2720750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2828072</t>
+          <t>2823808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5528400</t>
+          <t>5529828</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5663983</t>
+          <t>5664986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>48727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106591</t>
+          <t>110819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62177</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104990</t>
+          <t>102507</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>123353</t>
+          <t>123080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195573</t>
+          <t>196000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293396</t>
+          <t>289168</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>350987</t>
+          <t>351260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205982</t>
+          <t>208465</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248795</t>
+          <t>250707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515386</t>
+          <t>514959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587606</t>
+          <t>587879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68721</t>
+          <t>68253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111963</t>
+          <t>110814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74664</t>
+          <t>77830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>151006</t>
+          <t>151623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154682</t>
+          <t>159680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245864</t>
+          <t>244425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311584</t>
+          <t>312733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354826</t>
+          <t>355294</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360498</t>
+          <t>359881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>436840</t>
+          <t>433674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>689187</t>
+          <t>690626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>780369</t>
+          <t>775371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99442</t>
+          <t>99594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138584</t>
+          <t>138147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114316</t>
+          <t>116432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148144</t>
+          <t>149124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221673</t>
+          <t>224284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275385</t>
+          <t>277147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>397754</t>
+          <t>398191</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>436896</t>
+          <t>436744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392731</t>
+          <t>391751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>426559</t>
+          <t>424443</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>801828</t>
+          <t>800066</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>855540</t>
+          <t>852929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,18%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66370</t>
+          <t>64060</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227468</t>
+          <t>228936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135021</t>
+          <t>137532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180579</t>
+          <t>181728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182081</t>
+          <t>182796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>390532</t>
+          <t>389377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>658565</t>
+          <t>657097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>819663</t>
+          <t>821973</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>531651</t>
+          <t>530502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>577209</t>
+          <t>574698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1207731</t>
+          <t>1208886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1416182</t>
+          <t>1415467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97793</t>
+          <t>97915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132723</t>
+          <t>132673</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117014</t>
+          <t>115764</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146432</t>
+          <t>145508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224615</t>
+          <t>222863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269437</t>
+          <t>270785</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>428511</t>
+          <t>428561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463441</t>
+          <t>463319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399134</t>
+          <t>400058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>428552</t>
+          <t>429802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>837362</t>
+          <t>836014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>882184</t>
+          <t>883936</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52055</t>
+          <t>52278</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76141</t>
+          <t>76203</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132252</t>
+          <t>132223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>476270</t>
+          <t>456634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>189796</t>
+          <t>190718</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>638198</t>
+          <t>644090</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292024</t>
+          <t>291962</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>316110</t>
+          <t>315887</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131519</t>
+          <t>151155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>475537</t>
+          <t>475566</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>337756</t>
+          <t>331864</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>786158</t>
+          <t>785236</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48539</t>
+          <t>47593</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>68475</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108533</t>
+          <t>109716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>135341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163974</t>
+          <t>163054</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>199317</t>
+          <t>197476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>213108</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>234220</t>
+          <t>235166</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288658</t>
+          <t>289414</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316222</t>
+          <t>315039</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>508197</t>
+          <t>510038</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>543540</t>
+          <t>544460</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>527034</t>
+          <t>524524</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>749197</t>
+          <t>755954</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>871974</t>
+          <t>873901</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1578998</t>
+          <t>1535499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1504178</t>
+          <t>1526592</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2288957</t>
+          <t>2323565</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2708867</t>
+          <t>2702110</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2931030</t>
+          <t>2933540</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2074693</t>
+          <t>2118192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2781717</t>
+          <t>2779790</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4822798</t>
+          <t>4788190</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5607577</t>
+          <t>5585163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80104</t>
+          <t>80619</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117020</t>
+          <t>117236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95313</t>
+          <t>94277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128064</t>
+          <t>129115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186753</t>
+          <t>185613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234556</t>
+          <t>236467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377044</t>
+          <t>376828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413960</t>
+          <t>413445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>338485</t>
+          <t>337434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>371236</t>
+          <t>372272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>726057</t>
+          <t>724146</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773860</t>
+          <t>775000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92549</t>
+          <t>93131</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131353</t>
+          <t>132053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162625</t>
+          <t>161726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208996</t>
+          <t>209801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>265330</t>
+          <t>267936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327163</t>
+          <t>330792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>604136</t>
+          <t>603436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>642940</t>
+          <t>642358</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416498</t>
+          <t>415693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462869</t>
+          <t>463768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1033819</t>
+          <t>1030190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1095652</t>
+          <t>1093046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73625</t>
+          <t>71512</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109469</t>
+          <t>108437</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116219</t>
+          <t>116773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156631</t>
+          <t>158932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200867</t>
+          <t>200565</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257335</t>
+          <t>255838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528314</t>
+          <t>529346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>564158</t>
+          <t>566271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>533113</t>
+          <t>530812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>573525</t>
+          <t>572971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1070192</t>
+          <t>1071689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1126660</t>
+          <t>1126962</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65597</t>
+          <t>64972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98175</t>
+          <t>100438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86125</t>
+          <t>87380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122618</t>
+          <t>122259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156925</t>
+          <t>160058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208123</t>
+          <t>208624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>420972</t>
+          <t>418709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>453550</t>
+          <t>454175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393024</t>
+          <t>393383</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>429517</t>
+          <t>428262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>826666</t>
+          <t>826165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>877864</t>
+          <t>874731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49383</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78178</t>
+          <t>78116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72235</t>
+          <t>70206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102769</t>
+          <t>103979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127272</t>
+          <t>129347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174708</t>
+          <t>173090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308532</t>
+          <t>308594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337327</t>
+          <t>336710</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>301217</t>
+          <t>300007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>331751</t>
+          <t>333780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>615988</t>
+          <t>617606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>663424</t>
+          <t>661349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49318</t>
+          <t>48468</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75724</t>
+          <t>75946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80799</t>
+          <t>78217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112201</t>
+          <t>111633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136916</t>
+          <t>132107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177051</t>
+          <t>175351</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216859</t>
+          <t>216637</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243265</t>
+          <t>244115</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230733</t>
+          <t>231301</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262135</t>
+          <t>264717</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>458466</t>
+          <t>460166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498601</t>
+          <t>503410</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44093</t>
+          <t>44883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70887</t>
+          <t>69548</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87937</t>
+          <t>87594</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123787</t>
+          <t>122654</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139845</t>
+          <t>140257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183528</t>
+          <t>182837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>138996</t>
+          <t>140335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165790</t>
+          <t>165000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>210121</t>
+          <t>211254</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>245971</t>
+          <t>246314</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>360263</t>
+          <t>360954</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>403946</t>
+          <t>403534</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>515224</t>
+          <t>520496</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>602739</t>
+          <t>605763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>774864</t>
+          <t>772794</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>872861</t>
+          <t>869588</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1319432</t>
+          <t>1316431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1450792</t>
+          <t>1454107</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2672920</t>
+          <t>2669896</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2760435</t>
+          <t>2755163</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2505396</t>
+          <t>2508669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2603393</t>
+          <t>2605463</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5203123</t>
+          <t>5199808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5334483</t>
+          <t>5337484</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92812</t>
+          <t>91857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128253</t>
+          <t>129039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109773</t>
+          <t>111157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149749</t>
+          <t>149199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>210436</t>
+          <t>212774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>266115</t>
+          <t>264985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>324939</t>
+          <t>324153</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>360380</t>
+          <t>361335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280481</t>
+          <t>281031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>320457</t>
+          <t>319073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>617307</t>
+          <t>618437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>672986</t>
+          <t>670648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140935</t>
+          <t>140096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>186611</t>
+          <t>186964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>191318</t>
+          <t>188606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240973</t>
+          <t>237108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>342565</t>
+          <t>338293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408251</t>
+          <t>407159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500476</t>
+          <t>500123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>546152</t>
+          <t>546991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368314</t>
+          <t>372179</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>417969</t>
+          <t>420681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>888123</t>
+          <t>889215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>953809</t>
+          <t>958081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105464</t>
+          <t>105767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148163</t>
+          <t>148885</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147817</t>
+          <t>147684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195835</t>
+          <t>195003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>266597</t>
+          <t>262097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>330498</t>
+          <t>330152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532973</t>
+          <t>532251</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>575672</t>
+          <t>575369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>513837</t>
+          <t>514669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>561855</t>
+          <t>561988</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1060309</t>
+          <t>1060655</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1124210</t>
+          <t>1128710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81820</t>
+          <t>82498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118710</t>
+          <t>119165</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108998</t>
+          <t>107421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153180</t>
+          <t>151959</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200264</t>
+          <t>201122</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>258556</t>
+          <t>260968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>495907</t>
+          <t>495452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>532797</t>
+          <t>532119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>462060</t>
+          <t>463281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>506242</t>
+          <t>507819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>971301</t>
+          <t>968889</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1029593</t>
+          <t>1028735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>59967</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93200</t>
+          <t>92070</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86521</t>
+          <t>85472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123561</t>
+          <t>122373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153622</t>
+          <t>156452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203119</t>
+          <t>202566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336229</t>
+          <t>337359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>369087</t>
+          <t>369462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324239</t>
+          <t>325427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>361279</t>
+          <t>362328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>674110</t>
+          <t>674663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>723607</t>
+          <t>720777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43051</t>
+          <t>43003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73665</t>
+          <t>70942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76710</t>
+          <t>75714</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111620</t>
+          <t>109272</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126363</t>
+          <t>128549</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170467</t>
+          <t>173258</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235121</t>
+          <t>237844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265735</t>
+          <t>265783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242376</t>
+          <t>244724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277286</t>
+          <t>278282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492315</t>
+          <t>489524</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536419</t>
+          <t>534233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>61427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92249</t>
+          <t>93815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123389</t>
+          <t>123266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160588</t>
+          <t>161809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>197124</t>
+          <t>194347</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247137</t>
+          <t>245948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157602</t>
+          <t>156036</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>188424</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>228391</t>
+          <t>227170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>265590</t>
+          <t>265713</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>391693</t>
+          <t>392882</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>441706</t>
+          <t>444483</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>660984</t>
+          <t>653775</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>758293</t>
+          <t>753657</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>928969</t>
+          <t>931378</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1042891</t>
+          <t>1040224</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1614116</t>
+          <t>1617893</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1764599</t>
+          <t>1765029</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2665805</t>
+          <t>2670441</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2763114</t>
+          <t>2770323</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2512312</t>
+          <t>2514979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2626234</t>
+          <t>2623825</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5214702</t>
+          <t>5214272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5365185</t>
+          <t>5361408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75758</t>
+          <t>75036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112250</t>
+          <t>112040</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77246</t>
+          <t>78586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111739</t>
+          <t>113401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166434</t>
+          <t>163307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214114</t>
+          <t>211946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307213</t>
+          <t>307423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>343705</t>
+          <t>344427</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284016</t>
+          <t>282354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>318509</t>
+          <t>317169</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>601104</t>
+          <t>603272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>648784</t>
+          <t>651911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78363</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114630</t>
+          <t>116815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120073</t>
+          <t>121233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160943</t>
+          <t>161807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>208094</t>
+          <t>209598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>266653</t>
+          <t>265069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472654</t>
+          <t>470469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508921</t>
+          <t>507270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401716</t>
+          <t>400852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442586</t>
+          <t>441426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>883291</t>
+          <t>884875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941850</t>
+          <t>940346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90282</t>
+          <t>89485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130091</t>
+          <t>128201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124038</t>
+          <t>121821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163647</t>
+          <t>163156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221865</t>
+          <t>222270</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>280118</t>
+          <t>280347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536450</t>
+          <t>538340</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>576259</t>
+          <t>577056</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>496871</t>
+          <t>497362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536480</t>
+          <t>538697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1046941</t>
+          <t>1046712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1105194</t>
+          <t>1104789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73743</t>
+          <t>73149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110299</t>
+          <t>110814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97200</t>
+          <t>98206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137615</t>
+          <t>137699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181933</t>
+          <t>182778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239056</t>
+          <t>238542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>533716</t>
+          <t>533201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>570272</t>
+          <t>570866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>511462</t>
+          <t>511378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>551877</t>
+          <t>550871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1054036</t>
+          <t>1054550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1111159</t>
+          <t>1110314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58714</t>
+          <t>57350</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89471</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73130</t>
+          <t>72920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109664</t>
+          <t>109555</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>141031</t>
+          <t>139428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190189</t>
+          <t>189441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386520</t>
+          <t>385683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>417277</t>
+          <t>418641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>385366</t>
+          <t>385475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>421900</t>
+          <t>422110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>780832</t>
+          <t>781580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>829990</t>
+          <t>831593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44026</t>
+          <t>43806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71844</t>
+          <t>72832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64974</t>
+          <t>65417</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98735</t>
+          <t>98010</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116518</t>
+          <t>116272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>159494</t>
+          <t>159243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261548</t>
+          <t>260560</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289366</t>
+          <t>289586</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>277411</t>
+          <t>278136</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>311172</t>
+          <t>310729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>550044</t>
+          <t>550295</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>593020</t>
+          <t>593266</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>35140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57544</t>
+          <t>58379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80201</t>
+          <t>80199</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>119330</t>
+          <t>116697</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121168</t>
+          <t>121353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168099</t>
+          <t>167025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199454</t>
+          <t>198619</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>222461</t>
+          <t>221858</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>279568</t>
+          <t>282201</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318697</t>
+          <t>318699</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>487797</t>
+          <t>488871</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>534728</t>
+          <t>534543</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>521233</t>
+          <t>525366</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>605503</t>
+          <t>610908</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>714275</t>
+          <t>713789</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>817333</t>
+          <t>813841</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1256781</t>
+          <t>1264567</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1391939</t>
+          <t>1399609</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2778181</t>
+          <t>2772776</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2862451</t>
+          <t>2858318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2720750</t>
+          <t>2724242</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2823808</t>
+          <t>2824294</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5529828</t>
+          <t>5522158</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5664986</t>
+          <t>5657200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75878</t>
+          <t>73657</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48727</t>
+          <t>52243</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110819</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>81389</t>
+          <t>95039</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60265</t>
+          <t>72863</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102507</t>
+          <t>119117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>157267</t>
+          <t>168695</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>123080</t>
+          <t>137000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>196000</t>
+          <t>203519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>324109</t>
+          <t>334136</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289168</t>
+          <t>300732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>351260</t>
+          <t>355550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>229583</t>
+          <t>265249</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>208465</t>
+          <t>241171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250707</t>
+          <t>287425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>553692</t>
+          <t>599386</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514959</t>
+          <t>564562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587879</t>
+          <t>631081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310972</t>
+          <t>360288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>710959</t>
+          <t>768081</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>710959</t>
+          <t>768081</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>710959</t>
+          <t>768081</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88270</t>
+          <t>97465</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68253</t>
+          <t>74834</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110814</t>
+          <t>122231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>122761</t>
+          <t>130520</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77830</t>
+          <t>108266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>151623</t>
+          <t>150827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>211031</t>
+          <t>227986</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159680</t>
+          <t>200927</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>244425</t>
+          <t>265613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>335277</t>
+          <t>379425</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312733</t>
+          <t>354659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355294</t>
+          <t>402056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>388743</t>
+          <t>370563</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359881</t>
+          <t>350256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>433674</t>
+          <t>392817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>724020</t>
+          <t>749987</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690626</t>
+          <t>712360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>775371</t>
+          <t>777046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>117344</t>
+          <t>128613</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99594</t>
+          <t>109818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138147</t>
+          <t>151549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>130548</t>
+          <t>150967</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116432</t>
+          <t>134067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149124</t>
+          <t>170177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>247891</t>
+          <t>279580</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224284</t>
+          <t>252359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>277147</t>
+          <t>309479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>418994</t>
+          <t>492224</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398191</t>
+          <t>469288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>436744</t>
+          <t>511019</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>410327</t>
+          <t>469551</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391751</t>
+          <t>450341</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>424443</t>
+          <t>486451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>829322</t>
+          <t>961775</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>800066</t>
+          <t>931876</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>852929</t>
+          <t>988996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>540875</t>
+          <t>620518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>540875</t>
+          <t>620518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>540875</t>
+          <t>620518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077213</t>
+          <t>1241355</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077213</t>
+          <t>1241355</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077213</t>
+          <t>1241355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>158175</t>
+          <t>173286</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64060</t>
+          <t>152326</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228936</t>
+          <t>198420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>162048</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137532</t>
+          <t>159578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181728</t>
+          <t>195837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>320223</t>
+          <t>349959</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182796</t>
+          <t>321012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389377</t>
+          <t>382786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>727858</t>
+          <t>525361</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>657097</t>
+          <t>500227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>821973</t>
+          <t>546321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>550182</t>
+          <t>559521</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>530502</t>
+          <t>540357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>574698</t>
+          <t>576616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1278040</t>
+          <t>1084882</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1208886</t>
+          <t>1052055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1415467</t>
+          <t>1113829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886033</t>
+          <t>698647</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886033</t>
+          <t>698647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886033</t>
+          <t>698647</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712230</t>
+          <t>736194</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712230</t>
+          <t>736194</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712230</t>
+          <t>736194</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598263</t>
+          <t>1434841</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598263</t>
+          <t>1434841</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598263</t>
+          <t>1434841</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>115273</t>
+          <t>124955</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97915</t>
+          <t>108062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132673</t>
+          <t>146219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>130899</t>
+          <t>146779</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115764</t>
+          <t>130919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145508</t>
+          <t>163576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>246172</t>
+          <t>271734</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>222863</t>
+          <t>247056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>270785</t>
+          <t>296933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>445961</t>
+          <t>484391</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>428561</t>
+          <t>463127</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463319</t>
+          <t>501284</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>414667</t>
+          <t>461354</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400058</t>
+          <t>444557</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>429802</t>
+          <t>477214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>860627</t>
+          <t>945745</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836014</t>
+          <t>920546</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>883936</t>
+          <t>970423</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>64042</t>
+          <t>71884</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52278</t>
+          <t>61061</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76203</t>
+          <t>86249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>296532</t>
+          <t>102126</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132223</t>
+          <t>89463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>456634</t>
+          <t>115280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>360574</t>
+          <t>174010</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>190718</t>
+          <t>155951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>644090</t>
+          <t>192945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>304123</t>
+          <t>335196</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291962</t>
+          <t>320831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315887</t>
+          <t>346019</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>311257</t>
+          <t>336352</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>151155</t>
+          <t>323198</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>475566</t>
+          <t>349015</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>615380</t>
+          <t>671548</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>331864</t>
+          <t>652613</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>785236</t>
+          <t>689607</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975954</t>
+          <t>845558</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975954</t>
+          <t>845558</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975954</t>
+          <t>845558</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>63322</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47593</t>
+          <t>53021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68475</t>
+          <t>76882</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>122310</t>
+          <t>132625</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>109716</t>
+          <t>118953</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135341</t>
+          <t>148069</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>180251</t>
+          <t>195947</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163054</t>
+          <t>176384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197476</t>
+          <t>215046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>224818</t>
+          <t>246876</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>214284</t>
+          <t>233316</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>235166</t>
+          <t>257177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>302445</t>
+          <t>330847</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>289414</t>
+          <t>315403</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315039</t>
+          <t>344519</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>527263</t>
+          <t>577723</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>510038</t>
+          <t>558624</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>544460</t>
+          <t>597286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424755</t>
+          <t>463472</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424755</t>
+          <t>463472</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424755</t>
+          <t>463472</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707514</t>
+          <t>773670</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707514</t>
+          <t>773670</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707514</t>
+          <t>773670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>676924</t>
+          <t>733182</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>524524</t>
+          <t>680550</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>755954</t>
+          <t>786603</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1046486</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>873901</t>
+          <t>888878</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1535499</t>
+          <t>978948</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1723411</t>
+          <t>1667911</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1526592</t>
+          <t>1598604</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2323565</t>
+          <t>1743154</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2781140</t>
+          <t>2797610</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2702110</t>
+          <t>2744189</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2933540</t>
+          <t>2850242</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2607205</t>
+          <t>2793437</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2118192</t>
+          <t>2749218</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2779790</t>
+          <t>2839288</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5388344</t>
+          <t>5591047</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4788190</t>
+          <t>5515804</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5585163</t>
+          <t>5660354</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
